--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_012/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_012/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -394,6 +399,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -429,6 +439,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -460,6 +475,11 @@
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1296,17 +1316,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>SDR Bracket FE Model V&amp;V</t>
+          <t>SDR Bracket FEA V&amp;V</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Finite element structural analysis of Ti-6Al-4V AM SDR avionics bracket for PDR closeout</t>
+          <t>Ti-6Al-4V AM bracket finite element model for quasi-static and random vibration structural sizing</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Abaqus/2023 HF6 finite element model of the SDR avionics bracket (Ti-6Al-4V, additive manufactured, machined finish) used to confirm ≥0.20 margin on yield under worst-case combined static and dynamic (random vibration) loads, and to verify absence of local buckling at mounting ears. Outputs drive PDR closeout decisions on bolt sizing and fillet callouts.</t>
+          <t>Abaqus/2023 HF6 finite element model of the SDR avionics bracket (Ti-6Al-4V, AM build, machined finish) used to confirm margin on yield at worst-case combined static and dynamic stresses and to avoid local buckling at mounting ears, supporting PDR closeout. Valid for load set SYS-ENV-031 Rev D, temperatures 20-40 C, intact fasteners, and geometry at or above fillet callouts.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1321,12 +1341,12 @@
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>MRL 4</t>
+          <t>MRL 3</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
@@ -1344,9 +1364,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1465,7 +1485,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Yield Margin and Buckling Requirement</t>
+          <t>APL-STR-224 Rev C Acceptance Targets</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1475,7 +1495,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Model must confirm ≥0.20 margin of safety on yield at worst-case combined static + dynamic stresses, and predict no local buckling at mounting ears, to support PDR closeout per APL-STR-224 Rev C.</t>
+          <t>Analysis plan requirement: margin on yield ≥0.20 at worst-case combined static + dynamic stresses; no local buckling at mounting ears; correlated to test within documented uncertainty bands.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1497,12 +1517,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Abaqus/2023 HF6 FE Model — BRK-112</t>
+          <t>Abaqus/2023 HF6 FEA Model of BRK-112-A</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>316k-element quadratic-tet (C3D10) Abaqus model of Ti-6Al-4V SDR bracket including bolt preload contact, static and modal/random-vibration analyses.</t>
+          <t>316k-element C3D10 quadratic tet model of the Ti-6Al-4V SDR bracket; solves quasi-static limit loads and qualification random vibration; material and loads traceable to MMPDS-17 and SYS-ENV-031 Rev D.</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1539,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Engineering-unit shaker test (accelerometers and rosettes at F3 and L2) and 8.5 g static pull test providing modal frequencies and strain data for model validation.</t>
+          <t>Accelerometer and rosette measurements from engineering-unit shaker test and 8.5 g static pull test used for model validation; includes 3D scan geometry confirmation.</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1556,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>AM-lot coupon tests (n=8) for E and yield, and torque-tension calibration tests (n=12) for bolt preload uncertainty characterization (COV 11%).</t>
+          <t>AM lot coupon tensile data (n=8) confirming E and yield scatter per MMPDS-17; torque-tension tests (n=12) on hardware stack characterizing bolt preload COV=11%.</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1993,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Modal Frequency Correlation — Shaker Test</t>
+          <t>Modal Frequency Correlation</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1988,27 +2008,27 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>First two natural frequencies of FE model compared against accelerometer measurements on engineering-unit shaker test article.</t>
+          <t>First two natural frequencies of the bracket FEA model compared against shaker test measurements on the engineering unit with 3D-scan-confirmed geometry.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Measured first two bending modes from subcomponent shaker test</t>
+          <t>Subcomponent shaker test accelerometer data</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>If Yes, describe the method</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Percent difference reported; damping tuned to 1.6% from test data</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>4.3% error (mode 1), 3.1% error (mode 2)</t>
+          <t>Mode 1: 4.3% error; Mode 2: 3.1% error</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2020,7 +2040,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Random Vibration RMS Strain Correlation</t>
+          <t>Random Vibration Strain RMS Correlation</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2030,22 +2050,27 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Predicted RMS strain at fillet F3 and lug L2 during random vibration compared against rosette measurements after damping tuned to 1.6%.</t>
+          <t>Predicted RMS strain during random vibration at fillet F3 and lug L2 compared against rosette measurements from qualification shaker test after damping parameter tuning.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Measured RMS strain from shaker test rosettes</t>
+          <t>Shaker test rosette strain data at F3 and L2</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Damping uncertainty (±10% effect on vib RMS) included in combined error propagation</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>6.8% error after damping tuning</t>
+          <t>Strain RMS within 6.8% after damping tuning to 1.6%</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2057,7 +2082,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Static Pull Test Strain Correlation</t>
+          <t>Static Strain Correlation (8.5 g Pull Test)</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2067,22 +2092,27 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Predicted strain at fillet F3 under 8.5 g static pull compared against strain gauge measurements on engineering unit.</t>
+          <t>Predicted strain at fillet F3 under 8.5 g static pull compared against rosette measurement from static pull test on engineering unit.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Measured strain at F3 from 8.5 g static pull test</t>
+          <t>Static pull test rosette at F3</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Richardson extrapolation discretization error (2.4%), material scatter (3%), preload uncertainty (5%) propagated to margin uncertainty ΔMS ≈ ±0.05 (95%)</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>5.9% error</t>
+          <t>Strain at F3 within 5.9% of model</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2094,7 +2124,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study — Discretization Error</t>
+          <t>Mesh Convergence Study</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2104,12 +2134,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Three-mesh refinement study (160k, 316k, 620k elements); Richardson extrapolation applied to peak stress at F3 and first bending mode frequency.</t>
+          <t>Three-mesh refinement study (160k/316k/620k elements) assessing discretization error in peak stress at fillet F3 and first bending mode frequency via Richardson extrapolation.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation-estimated exact solution</t>
+          <t>Richardson extrapolation extrapolated solution</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2124,7 +2154,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>2.4% discretization error at F3; 1.8% for first bending mode</t>
+          <t>Peak stress F3 discretization error 2.4%; first bending mode 1.8%</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2136,7 +2166,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Independent Peer Review — Stress and Lug Check</t>
+          <t>Independent Peer Review and Hand Check</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2146,12 +2176,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Independent analyst reproduced mid-mesh case and performed hand lug check per MIL-HDBK-5; compared F3 stress and bearing stress margin of safety.</t>
+          <t>Independent analyst reproduced mid-mesh F3 stress and performed MIL-HDBK-5 hand lug bearing stress check to verify model setup and post-processing.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Independent FEA replication and MIL-HDBK-5 hand calculation</t>
+          <t>Independent hand calculation (MIL-HDBK-5 bearing stress)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2161,7 +2191,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>F3 stress match within 2.2%; bearing MS 0.41 (hand) vs 0.38 (FEA)</t>
+          <t>F3 stress match within 2.2%; bearing stress MS: hand calc 0.41 vs FEA 0.38</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2308,19 +2338,19 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented benchmark suite reproduced in-house; configuration management and environment capture in place.</t>
+          <t>Commercial solver with documented benchmarks; version control; repeatable results</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Abaqus/2023 HF6 is a commercial solver. NAFEMS benchmarks LE10, BEAM3, and axisymmetric pressure vessel reproduced in-house within 1–2% using production templates. Model and run decks tracked in Git (tag v0.9.7); conda env export captures solver version and environment. Pre/post scripts passed unit tests; QA checklist STR-CHK-05 signed; no open NCRs. Training records for both analysts current (2024).</t>
+          <t>Abaqus/2023 HF6 used; NAFEMS benchmark problems LE10, BEAM3, and Axisymmetric pressure vessel reproduced in-house within 1-2% using project templates. Model, scripts, and run decks tracked in Git (repo STR/BRK-112, tag v0.9.7); solver version and environment captured via conda env export; mesh seeds scripted in Python. Runs repeatable on independent platform (Windows 11) within 0.8% for stresses. Pre/post scripts passed unit tests; checklist STR-CHK-05 signed; no open NCRs. All artifacts archived at \\nas\STR\BRK-112\release\v0.9.7.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2345,16 +2375,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code verified against known analytical or benchmark solutions within acceptable tolerance.</t>
+          <t>Benchmark problems demonstrate code correctly solves governing equations</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>NAFEMS benchmarks LE10, BEAM3, and axisymmetric pressure vessel reproduced within 1–2% in-house. Reduced vs full integration comparison yielded &lt;1.5% stress difference with no hourglassing. No method of manufactured solutions reported, but benchmark coverage is adequate for the physics regime.</t>
+          <t>NAFEMS standard benchmark problems (LE10 linear elastic patch test, BEAM3, Axisymmetric pressure vessel) reproduced in-house within 1-2% against reference solutions using project templates. Reduced vs full integration comparison gave &lt;1.5% stress difference at hot spots with no hourglassing, confirming element formulation correctness.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2376,19 +2406,19 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with quantified GCI or Richardson extrapolation error below acceptable threshold.</t>
+          <t>Mesh convergence demonstrated with quantified discretization error</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three-mesh study (160k/316k/620k elements). Peak stress at F3 changed 6.1% (coarse→mid) and 2.7% (mid→fine). Richardson extrapolation gives 2.4% discretization error at F3 and 1.8% for first bending mode. Final mesh selected at 316k provides adequate convergence with quantified residual error used in uncertainty propagation.</t>
+          <t>Three-mesh study (160k/316k/620k C3D10 elements) performed. Peak stress at F3: 6.1% change coarse-to-mid, 2.7% mid-to-fine. Richardson extrapolation applied, yielding 2.4% discretization error at F3 and 1.8% for first bending mode. Mid-mesh (316k) selected as production mesh with quantified error contribution to margin uncertainty propagation.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2417,12 +2447,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Solver convergence monitored with residual and force-balance targets met.</t>
+          <t>Solver convergence demonstrated with residual targets and force balance</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Static nonlinear solves converged in &lt;12 Newton-Raphson iterations; force balance within 0.6%. Modal extraction via Lanczos with frequency residuals &lt;0.5%. Iterative convergence is well-documented and within tight tolerances.</t>
+          <t>Static solves converged in fewer than 12 Newton-Raphson iterations; force balance within 0.6%. Modal extraction using Lanczos with frequency residuals &lt;0.5%. Element formulation check (reduced vs full integration) showed &lt;1.5% stress difference confirming solver stability.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2444,19 +2474,19 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review of model setup, boundary conditions, and post-processing; signed QA checklist.</t>
+          <t>Independent review of model setup; boundary condition and mesh quality checks</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Independent analyst repeated mid-mesh case and matched F3 stress within 2.2%. Hand lug check per MIL-HDBK-5 performed independently. QA checklist STR-CHK-05 signed; boundary conditions traced to load spec SYS-ENV-031 Rev D; geometry imports confirmed against CAD BRK-112-A Rev B via 3D scan of engineering unit.</t>
+          <t>Independent analyst reproduced the mid-mesh case and matched F3 stress within 2.2%. MIL-HDBK-5 hand lug bearing stress check performed (MS 0.41 hand vs 0.38 FEA). Checklist STR-CHK-05 signed. Inputs trace to PLM items (CAD Rev B), materials database MD-017, and load spec SYS-ENV-031 Rev D via RunLog.xlsx with seeds and checksums. Training records for both analysts current (2024).</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2485,12 +2515,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and modeling assumptions documented and justified for the intended physics regime.</t>
+          <t>Governing equations justified; simplifications and limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Linear elastic model justified for margin check against yield (no plasticity required). Quadratic tet elements (C3D10) appropriate for stress concentration capture. Contact via surface-to-surface hard contact with bolt pretension sections. AM porosity captured via MMPDS allowables knockdown rather than explicit modeling — limitation documented. Thermal and fretting effects explicitly scoped out with applicability envelope stated.</t>
+          <t>10-node quadratic tet (C3D10) elastic formulation selected; elastic-only response appropriate for below-yield sizing. Surface-to-surface hard contact with bolt pretension sections used for bolt interfaces. Structural damping 1.5% from prior bracket family tests, tuned to 1.6% against test data. Documented simplifications: no thermal load, no fretting wear, AM porosity captured in material allowables knockdown rather than explicit meshing. AM surface waviness not meshed. Applicability envelope explicitly bounded.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2512,19 +2542,19 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, loads, and boundary conditions from traceable, tested sources with uncertainty characterization.</t>
+          <t>Material properties and boundary conditions from measurements with uncertainty characterization</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>E = 113 ± 3 GPa and σy = 880 ± 20 MPa from MMPDS-17, confirmed by AM-lot coupon tests (n=8). A-basis yield used for margins. Bolt preload 6.5 ± 0.7 kN from torque-tension tests (n=12, COV 11%). Static accelerations from SYS-ENV-031 Rev D (±10.2 g). Random vibration PSD per GEVS 2.5.2. Damping 1.5% from prior bracket family tests. All inputs traced to PLM items, materials database MD-017, and load spec.</t>
+          <t>Ti-6Al-4V E = 113 ± 3 GPa and σy = 880 ± 20 MPa from MMPDS-17, confirmed by AM lot coupons (n=8). A-basis yield used for margins. Bolt preload 6.5 ± 0.7 kN from torque-tension calibration (n=12, COV=11%). Static accelerations per SYS-ENV-031 Rev D; random vibration PSD per GEVS 2.5.2. All inputs traceable to PLM and materials database MD-017. Sensitivity studies performed for ±10% thickness, ±0.5 mm fillet, ±15% preload, ±3% E.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2553,12 +2583,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test articles representative of the production configuration with documented sample characterization.</t>
+          <t>Test articles are production-representative; sample size documented</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Validation performed on a single engineering unit with 3D scans confirming geometry against CAD. Material coupons from the same AM lot (n=8) characterize batch properties. Bolt preload tested on the actual hardware stack (n=12). Only one structural test article reported; no statistical characterization of test-article population.</t>
+          <t>Validation performed on an engineering unit bracket with 3D scans confirming geometry matches CAD BRK-112-A Rev B. AM lot coupons (n=8) and bolt hardware stack (n=12) tested. Sample sizes are modest but with statistical characterization (COV reported for preload). Engineering unit is described as representative but is not explicitly a production article.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2587,12 +2617,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions controlled and measured with calibrated instruments; environmental conditions documented.</t>
+          <t>Test conditions controlled and measured with calibrated instruments; measurement uncertainty reported</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Accelerometers and rosette strain gauges used at F3 and L2. Shaker test conducted per GEVS 2.5.2 conditions (60 s/axis). Static pull to 8.5 g applied and measured. Instrument calibration records not explicitly cited in the report but professional test execution is implied. Temperature range for validity stated (20–40 C) but environmental control during test not explicitly described.</t>
+          <t>Accelerometers and strain rosettes used at fillet F3 and lug L2 during shaker and static pull tests. Random vibration per GEVS 2.5.2, Q=10, 60 s/axis. Static pull to 8.5 g. Instrument calibration and environmental control are not explicitly detailed in the report, but test conditions are described as matching analysis specs (SYS-ENV-031 Rev D). Measurement uncertainty is implicitly included in error bands but not explicitly quoted as a separate measurement uncertainty value.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2614,19 +2644,19 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs matched to experimental test conditions with uncertainty propagation documented.</t>
+          <t>Model inputs confirmed to match experimental test conditions</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Damping tuned from 1.5% to 1.6% after correlation to shaker test — adjustment documented and physically justified. Geometry confirmed via 3D scan of engineering unit. Load levels in validation test (8.5 g static) differ from qualification loads (10.2 g), representing a partial coverage gap. Input uncertainties (preload, E, fillet) characterized and propagated, but explicit comparison table of model inputs vs. test-measured conditions is not provided.</t>
+          <t>Static accelerations in the model correspond to the 8.5 g pull test level; random vibration PSD matches GEVS 2.5.2 as applied in test. Geometry confirmed via 3D scan of engineering unit against CAD Rev B. Bolt preload in model (6.5 ± 0.7 kN) derived from the same hardware stack tested. Damping updated from 1.5% to 1.6% to match test-measured response. Explicit uncertainty propagation from input parameter mismatches is not separately documented beyond the sensitivity study.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2648,19 +2678,19 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to test data at multiple locations with uncertainty bands.</t>
+          <t>Quantitative comparison of model predictions to test data with uncertainty bands at multiple points</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Modal frequencies compared at two modes (4.3%, 3.1% errors). RMS strain during random vibration compared at sensor locations (6.8%). Static strain at F3 compared against pull test (5.9%). Independent hand check of bearing stress MS (0.41 vs 0.38). Combined uncertainty band on final margin ΔMS = ±0.05 at 95% confidence propagated from mesh, material, preload, and damping contributions via linearization.</t>
+          <t>Multiple QoIs compared: Mode 1 frequency 4.3% error, Mode 2 frequency 3.1% error, strain RMS during vib within 6.8%, static strain at F3 within 5.9%. Combined uncertainty propagated to margin: ΔMS ≈ ±0.05 at 95% confidence from mesh (2.4%), material (3%), preload (5%), damping (10% effect on vib RMS) contributions. Worst-case static+vib stress 684 MPa vs A-basis yield 880 MPa, mean MS=0.29. Independent hand check bearing stress MS 0.41 (hand) vs 0.38 (FEA). Multiple comparison points (F3 and L2) across multiple loading conditions.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2682,19 +2712,19 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly address the safety/performance decision and are measurable both computationally and experimentally.</t>
+          <t>QoIs directly address the safety/performance decision and are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>QoIs are peak von Mises at fillet F3 (directly tied to yield margin requirement ≥0.20 MS), bearing stress at lug L2, first four natural frequencies, and RMS stress during random vibration. These map directly to the PDR closeout decision criteria. All QoIs were measurable experimentally (rosettes at F3/L2, accelerometers for frequencies) and computationally.</t>
+          <t>QoIs are peak von Mises at fillet F3, bearing stress at lug L2, first four natural frequencies, RMS stress during random vibration, and margin of safety with uncertainty bands — directly addressing the APL-STR-224 requirement for ≥0.20 MS and no local buckling. All QoIs are measurable experimentally (strain rosettes, accelerometers) and computationally. Eigenvalue buckling factor (2.9) addresses buckling requirement directly.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2716,19 +2746,19 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation activities cover the same geometry, load regime, and operating conditions as the intended use.</t>
+          <t>Validation conditions match intended use geometry, loading, and physics regime</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation performed on the actual bracket engineering unit with geometry confirmed by 3D scan. Shaker test per GEVS 2.5.2 matches the intended random vibration load specification. Static pull to 8.5 g validates static response but is below the 10.2 g qualification level, representing a partial extrapolation gap. AM surface waviness not explicitly modeled; applicability envelope explicitly limits reuse to intact fasteners, 20–40 C, and geometry at or above fillet callouts. Gaps are documented and bounded by uncertainty analysis.</t>
+          <t>Validation performed on the same bracket geometry (3D-scan-confirmed) under loading conditions consistent with SYS-ENV-031 Rev D. Both quasi-static and random vibration regimes validated. Applicability envelope explicitly stated: load set SYS-ENV-031 Rev D, temperatures 20-40 C, intact fasteners, geometry at or above fillet callouts. Gaps noted: AM surface waviness not explicitly modeled; no thermal distortion validation; no fretting/wear validation; engineering unit rather than production article used. Temperature range (20-40 C) not explicitly validated across full envelope.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2913,7 +2943,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The Abaqus/2023 HF6 model of the Ti-6Al-4V SDR bracket meets all acceptance targets defined in APL-STR-224 Rev C. Worst-case margin of safety at F3 is MS = 0.29 ± 0.05 (95%), exceeding the ≥0.20 requirement with margin. Natural frequencies, buckling factor, and bearing stress margins are all within requirements. Numerical discretization error is quantified (2.4%), solver convergence is tight (&lt;0.6% force balance), and an independent peer review confirmed results within 2.2%. Validation against shaker and static pull tests shows agreement within 4.3–6.8% across all comparison QoIs. Combined uncertainty propagation bounds the margin conservatively. Applicability is restricted to load set SYS-ENV-031 Rev D, temperatures 20–40 C, intact fasteners, and geometry at or above fillet callouts; any changes trigger re-verification per APL-STR-224. Model is fit-for-purpose for PDR closeout and for finalizing bolt sizing and fillet callouts.</t>
+          <t>The SDR bracket FEA model meets all APL-STR-224 Rev C acceptance targets. Worst-case margin of safety at fillet F3 is 0.29 ± 0.05 (95%), exceeding the required ≥0.20 threshold. First four modes are above 1.25× instrument notch frequencies. Eigenvalue buckling factor is 2.9 on ears. Numerical errors are quantified and bounded (discretization 2.4%, solver force balance 0.6%). Model inputs are traceable to tested material and hardware data with uncertainty characterization. Validation against engineering-unit shaker and static tests shows frequency errors of 3.1-4.3% and strain errors of 5.9-6.8%, within documented acceptance criteria. Independent peer review confirmed results. Configuration management and provenance are complete. Model is accepted for PDR closeout and bolt sizing/fillet callout finalization within the stated applicability envelope (load set SYS-ENV-031 Rev D, 20-40 C, intact fasteners, geometry at or above fillet callouts). Any geometry or load changes beyond this envelope require re-verification per APL-STR-224. Assessment applies pending update for final CAD Rev C when released.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
